--- a/templates/Template_10_Contracts.xlsx
+++ b/templates/Template_10_Contracts.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,12 +33,16 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <i val="1"/>
-      <color rgb="00926B18"/>
+      <color rgb="00999999"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -49,12 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001B4965"/>
         <bgColor rgb="001B4965"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,12 +82,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,7 +458,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -605,9 +604,9 @@
       <c r="J2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
@@ -618,28 +617,34 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="N2" s="2" t="n">
-        <v>4</v>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="O2" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="P2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>3</v>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PART</t>
+          <t>OVR6</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Part-Time Contract</t>
+          <t>Approved 6-Period Overload</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -658,55 +663,61 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
-        <v>2</v>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>DEPT</t>
+          <t>PART</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Department Head Contract</t>
+          <t>Part-Time Contract</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -725,44 +736,50 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="N4" s="2" t="n">
-        <v>3</v>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
   </sheetData>
